--- a/smd-process-control/tests/fixtures/production-sample.xlsx
+++ b/smd-process-control/tests/fixtures/production-sample.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27.07" sheetId="1" r:id="R233aacade04c4841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25.07" sheetId="1" r:id="R8f4886b525cb44de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -271,8 +271,6 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
@@ -296,355 +294,1003 @@
     <x:col min="23" max="23" width="14" hidden="0" customWidth="1"/>
     <x:col min="24" max="24" width="14" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="14" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="14" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="14" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="14" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="14" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="14" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="14" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="14" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="14" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="14" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="14" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="14" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="14" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="14" hidden="0" customWidth="1"/>
+    <x:col min="39" max="39" width="14" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="14" hidden="0" customWidth="1"/>
+    <x:col min="41" max="41" width="14" hidden="0" customWidth="1"/>
+    <x:col min="42" max="42" width="14" hidden="0" customWidth="1"/>
+    <x:col min="43" max="43" width="14" hidden="0" customWidth="1"/>
+    <x:col min="44" max="44" width="14" hidden="0" customWidth="1"/>
+    <x:col min="45" max="45" width="14" hidden="0" customWidth="1"/>
+    <x:col min="46" max="46" width="14" hidden="0" customWidth="1"/>
+    <x:col min="47" max="47" width="14" hidden="0" customWidth="1"/>
+    <x:col min="48" max="48" width="14" hidden="0" customWidth="1"/>
+    <x:col min="49" max="49" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="3" t="str">
-        <x:v>SẢN LƯỢNG TỪNG TIME 27/07/2026</x:v>
-      </x:c>
+      <x:c r="C2" s="3" t="str">
+        <x:v>BÁO CÁO SẢN LƯỢNG CÁC CÔNG ĐOẠN SMD THEO TIME NGÀY 25/07/2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="C3" s="7" t="str">
+        <x:v>Ngày</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>Ca</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="F3" s="7"/>
+      <x:c r="G3" s="7" t="str">
+        <x:v>CAPA</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="I3" s="7"/>
+      <x:c r="J3" s="7" t="str">
+        <x:v>CAPA</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="L3" s="7"/>
+      <x:c r="M3" s="7"/>
+      <x:c r="N3" s="3" t="str">
+        <x:v>Sản Lượng Từng Time</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="C4" s="7"/>
+      <x:c r="D4" s="7"/>
+      <x:c r="E4" s="7"/>
+      <x:c r="F4" s="7"/>
+      <x:c r="G4" s="7"/>
+      <x:c r="H4" s="7"/>
+      <x:c r="I4" s="7"/>
+      <x:c r="J4" s="7"/>
+      <x:c r="K4" s="7" t="str">
+        <x:v>CAPA</x:v>
+      </x:c>
+      <x:c r="L4" s="7" t="str">
+        <x:v>Sản Lượng Thực Tế</x:v>
+      </x:c>
+      <x:c r="M4" s="7" t="str">
+        <x:v>Tỷ Lệ</x:v>
+      </x:c>
+      <x:c r="N4" s="7" t="str">
+        <x:v>Time A</x:v>
+      </x:c>
+      <x:c r="O4" s="7" t="str">
+        <x:v>Time A</x:v>
+      </x:c>
+      <x:c r="P4" s="7" t="str">
+        <x:v>Time A</x:v>
+      </x:c>
+      <x:c r="Q4" s="7" t="str">
+        <x:v>Time A</x:v>
+      </x:c>
+      <x:c r="R4" s="7" t="str">
+        <x:v>Time A</x:v>
+      </x:c>
+      <x:c r="S4" s="7" t="str">
+        <x:v>Time B</x:v>
+      </x:c>
+      <x:c r="T4" s="7" t="str">
+        <x:v>Time B</x:v>
+      </x:c>
+      <x:c r="U4" s="7" t="str">
+        <x:v>Time B</x:v>
+      </x:c>
+      <x:c r="V4" s="7" t="str">
+        <x:v>Time B</x:v>
+      </x:c>
+      <x:c r="W4" s="7" t="str">
+        <x:v>Time B</x:v>
+      </x:c>
+      <x:c r="X4" s="7" t="str">
+        <x:v>Time C</x:v>
+      </x:c>
+      <x:c r="Y4" s="7" t="str">
+        <x:v>Time C</x:v>
+      </x:c>
+      <x:c r="Z4" s="7" t="str">
+        <x:v>Time C</x:v>
+      </x:c>
+      <x:c r="AA4" s="7" t="str">
+        <x:v>Time C</x:v>
+      </x:c>
+      <x:c r="AB4" s="7" t="str">
+        <x:v>Time C</x:v>
+      </x:c>
+      <x:c r="AC4" s="7" t="str">
+        <x:v>Time D</x:v>
+      </x:c>
+      <x:c r="AD4" s="7" t="str">
+        <x:v>Time D</x:v>
+      </x:c>
+      <x:c r="AE4" s="7" t="str">
+        <x:v>Time D</x:v>
+      </x:c>
+      <x:c r="AF4" s="7" t="str">
+        <x:v>Time D</x:v>
+      </x:c>
+      <x:c r="AG4" s="7" t="str">
+        <x:v>Time D</x:v>
+      </x:c>
+      <x:c r="AH4" s="7" t="str">
+        <x:v>Time E</x:v>
+      </x:c>
+      <x:c r="AI4" s="7" t="str">
+        <x:v>Time E</x:v>
+      </x:c>
+      <x:c r="AJ4" s="7" t="str">
+        <x:v>Time E</x:v>
+      </x:c>
+      <x:c r="AK4" s="7" t="str">
+        <x:v>Time E</x:v>
+      </x:c>
+      <x:c r="AL4" s="7" t="str">
+        <x:v>Time E</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="C5" s="7"/>
+      <x:c r="D5" s="7"/>
+      <x:c r="E5" s="7"/>
+      <x:c r="F5" s="7"/>
+      <x:c r="G5" s="7"/>
+      <x:c r="H5" s="7"/>
+      <x:c r="I5" s="7"/>
+      <x:c r="J5" s="7"/>
+      <x:c r="K5" s="7" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L5" s="7"/>
+      <x:c r="M5" s="7"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="7" t="str">
-        <x:v>Date</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="str">
-        <x:v>Shift</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="str">
-        <x:v>Line</x:v>
-      </x:c>
-      <x:c r="D6" s="7" t="str">
-        <x:v>Model</x:v>
-      </x:c>
-      <x:c r="E6" s="7" t="str">
-        <x:v>Process</x:v>
-      </x:c>
-      <x:c r="F6" s="7" t="str">
-        <x:v>Time A CAPA</x:v>
-      </x:c>
-      <x:c r="G6" s="7" t="str">
-        <x:v>Time A Actual</x:v>
-      </x:c>
-      <x:c r="H6" s="7" t="str">
-        <x:v>Time A Downtime</x:v>
-      </x:c>
-      <x:c r="I6" s="7" t="str">
-        <x:v>Time A Note</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="str">
-        <x:v>Time B CAPA</x:v>
-      </x:c>
+      <x:c r="C6" s="7"/>
+      <x:c r="D6" s="7"/>
+      <x:c r="E6" s="7"/>
+      <x:c r="F6" s="7"/>
+      <x:c r="G6" s="7"/>
+      <x:c r="H6" s="7"/>
+      <x:c r="I6" s="7"/>
+      <x:c r="J6" s="7"/>
       <x:c r="K6" s="7" t="str">
-        <x:v>Time B Actual</x:v>
+        <x:v>CAPA</x:v>
       </x:c>
       <x:c r="L6" s="7" t="str">
-        <x:v>Time B Downtime</x:v>
+        <x:v>Sản Lượng Thực Tế</x:v>
       </x:c>
       <x:c r="M6" s="7" t="str">
-        <x:v>Time B Note</x:v>
+        <x:v>Tỷ Lệ</x:v>
       </x:c>
       <x:c r="N6" s="7" t="str">
-        <x:v>Time C CAPA</x:v>
+        <x:v>CAPA</x:v>
       </x:c>
       <x:c r="O6" s="7" t="str">
-        <x:v>Time C Actual</x:v>
+        <x:v>Sản Lượng Thực Tế</x:v>
       </x:c>
       <x:c r="P6" s="7" t="str">
-        <x:v>Time C Downtime</x:v>
+        <x:v>Tỷ Lệ</x:v>
       </x:c>
       <x:c r="Q6" s="7" t="str">
-        <x:v>Time C Note</x:v>
+        <x:v>Time dừng máy (p)</x:v>
       </x:c>
       <x:c r="R6" s="7" t="str">
-        <x:v>Time D CAPA</x:v>
+        <x:v>Ghi chú</x:v>
       </x:c>
       <x:c r="S6" s="7" t="str">
-        <x:v>Time D Actual</x:v>
+        <x:v>CAPA</x:v>
       </x:c>
       <x:c r="T6" s="7" t="str">
-        <x:v>Time D Downtime</x:v>
+        <x:v>Sản Lượng Thực Tế</x:v>
       </x:c>
       <x:c r="U6" s="7" t="str">
-        <x:v>Time D Note</x:v>
+        <x:v>Tỷ Lệ</x:v>
       </x:c>
       <x:c r="V6" s="7" t="str">
-        <x:v>Time E CAPA</x:v>
+        <x:v>Time dừng máy (p)</x:v>
       </x:c>
       <x:c r="W6" s="7" t="str">
-        <x:v>Time E Actual</x:v>
+        <x:v>Ghi chú</x:v>
       </x:c>
       <x:c r="X6" s="7" t="str">
-        <x:v>Time E Downtime</x:v>
+        <x:v>CAPA</x:v>
       </x:c>
       <x:c r="Y6" s="7" t="str">
-        <x:v>Time E Note</x:v>
+        <x:v>Sản Lượng Thực Tế</x:v>
+      </x:c>
+      <x:c r="Z6" s="7" t="str">
+        <x:v>Tỷ Lệ</x:v>
+      </x:c>
+      <x:c r="AA6" s="7" t="str">
+        <x:v>Time dừng máy (p)</x:v>
+      </x:c>
+      <x:c r="AB6" s="7" t="str">
+        <x:v>Ghi chú</x:v>
+      </x:c>
+      <x:c r="AC6" s="7" t="str">
+        <x:v>CAPA</x:v>
+      </x:c>
+      <x:c r="AD6" s="7" t="str">
+        <x:v>Sản Lượng Thực Tế</x:v>
+      </x:c>
+      <x:c r="AE6" s="7" t="str">
+        <x:v>Tỷ Lệ</x:v>
+      </x:c>
+      <x:c r="AF6" s="7" t="str">
+        <x:v>Time dừng máy (p)</x:v>
+      </x:c>
+      <x:c r="AG6" s="7" t="str">
+        <x:v>Ghi chú</x:v>
+      </x:c>
+      <x:c r="AH6" s="7" t="str">
+        <x:v>CAPA</x:v>
+      </x:c>
+      <x:c r="AI6" s="7" t="str">
+        <x:v>Sản Lượng Thực Tế</x:v>
+      </x:c>
+      <x:c r="AJ6" s="7" t="str">
+        <x:v>Tỷ Lệ</x:v>
+      </x:c>
+      <x:c r="AK6" s="7" t="str">
+        <x:v>Time dừng máy (p)</x:v>
+      </x:c>
+      <x:c r="AL6" s="7" t="str">
+        <x:v>Ghi chú</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>27.07.2026</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="C7"/>
+      <x:c r="D7" t="str">
         <x:v>DAY</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="E7" t="str">
         <x:v>Line 1</x:v>
       </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="F7" t="str">
         <x:v>MODEL-A</x:v>
       </x:c>
-      <x:c r="E7" t="str">
-        <x:v>Router</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="G7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="O7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I7" t="str">
+      <x:c r="P7" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="Q7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R7" t="str">
         <x:v>setup</x:v>
       </x:c>
-      <x:c r="J7" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K7" t="n">
+      <x:c r="S7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="U7" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="V7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W7"/>
+      <x:c r="X7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Y7" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M7"/>
-      <x:c r="N7" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="O7" t="n">
+      <x:c r="Z7" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AA7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB7"/>
+      <x:c r="AC7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AD7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AE7" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AF7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG7"/>
+      <x:c r="AH7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AI7" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q7"/>
-      <x:c r="R7" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U7"/>
-      <x:c r="V7" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="W7" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y7"/>
+      <x:c r="AJ7" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AK7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>27.07.2026</x:v>
-      </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="C8"/>
+      <x:c r="D8" t="str">
         <x:v>DAY</x:v>
       </x:c>
-      <x:c r="C8" t="str">
+      <x:c r="E8" t="str">
         <x:v>Line 2</x:v>
       </x:c>
-      <x:c r="D8" t="str">
+      <x:c r="F8" t="str">
         <x:v>MODEL-B</x:v>
       </x:c>
-      <x:c r="E8" t="str">
-        <x:v>Xray</x:v>
-      </x:c>
-      <x:c r="F8" t="n">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="G8" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H8" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H8"/>
       <x:c r="I8"/>
       <x:c r="J8" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K8" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="O8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P8" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="Q8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R8" t="str">
+        <x:v>setup</x:v>
+      </x:c>
+      <x:c r="S8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="U8" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="V8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W8"/>
+      <x:c r="X8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Y8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M8"/>
-      <x:c r="N8" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="O8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="P8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q8"/>
-      <x:c r="R8" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S8" t="n">
+      <x:c r="Z8" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AA8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB8"/>
+      <x:c r="AC8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AD8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AE8" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AF8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG8"/>
+      <x:c r="AH8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AI8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="T8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U8"/>
-      <x:c r="V8" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="W8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="X8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y8"/>
+      <x:c r="AJ8" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AK8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>27.07.2026</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
+      <x:c r="C9"/>
+      <x:c r="D9" t="str">
         <x:v>DAY</x:v>
       </x:c>
-      <x:c r="C9" t="str">
-        <x:v>Router Máy 2</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
+      <x:c r="E9" t="str">
+        <x:v>Line 3</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
         <x:v>MODEL-A</x:v>
       </x:c>
-      <x:c r="E9" t="str">
-        <x:v>Router</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="G9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H9" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H9"/>
       <x:c r="I9"/>
       <x:c r="J9" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K9" t="n">
-        <x:v>1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M9"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
       <x:c r="N9" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="O9"/>
-      <x:c r="P9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q9"/>
-      <x:c r="R9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S9"/>
+      <x:c r="O9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R9" t="str">
+        <x:v>setup</x:v>
+      </x:c>
+      <x:c r="S9" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="T9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U9"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="U9" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
       <x:c r="V9" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W9"/>
       <x:c r="X9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y9"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Y9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="Z9" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AA9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB9"/>
+      <x:c r="AC9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AD9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AE9" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AF9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG9"/>
+      <x:c r="AH9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AI9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AJ9" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AK9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>27.07.2026</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>Total</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>TOTAL</x:v>
-      </x:c>
-      <x:c r="D10"/>
+      <x:c r="C10"/>
+      <x:c r="D10" t="str">
+        <x:v>DAY</x:v>
+      </x:c>
       <x:c r="E10" t="str">
-        <x:v>XRAY</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
-        <x:v>10</x:v>
+        <x:v>Line 4</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>MODEL-B</x:v>
       </x:c>
       <x:c r="G10" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H10" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H10"/>
       <x:c r="I10"/>
       <x:c r="J10" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K10" t="n">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M10" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
       <x:c r="N10" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="O10" t="n">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="P10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q10"/>
-      <x:c r="R10" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P10" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="Q10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R10" t="str">
+        <x:v>setup</x:v>
       </x:c>
       <x:c r="S10" t="n">
-        <x:v>99</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="T10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U10"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="U10" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
       <x:c r="V10" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="W10" t="n">
-        <x:v>99</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W10"/>
       <x:c r="X10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y10"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Y10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="Z10" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AA10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB10"/>
+      <x:c r="AC10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AD10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AE10" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AF10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG10"/>
+      <x:c r="AH10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AI10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AJ10" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AK10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="C11"/>
+      <x:c r="D11" t="str">
+        <x:v>DAY</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>Xray-1</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>MODEL-A</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="O11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P11" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="Q11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R11" t="str">
+        <x:v>setup</x:v>
+      </x:c>
+      <x:c r="S11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="U11" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="V11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W11"/>
+      <x:c r="X11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Y11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="Z11" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AA11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB11"/>
+      <x:c r="AC11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AD11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AE11" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AF11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG11"/>
+      <x:c r="AH11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AI11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AJ11" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AK11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="C12"/>
+      <x:c r="D12" t="str">
+        <x:v>DAY</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>ICT #1</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>MODEL-B</x:v>
+      </x:c>
+      <x:c r="G12" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="O12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P12" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="Q12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R12" t="str">
+        <x:v>setup</x:v>
+      </x:c>
+      <x:c r="S12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T12" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="U12" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="V12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W12"/>
+      <x:c r="X12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Y12" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="Z12" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AA12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB12"/>
+      <x:c r="AC12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AD12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AE12" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AF12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG12"/>
+      <x:c r="AH12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AI12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AJ12" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AK12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="C13"/>
+      <x:c r="D13" t="str">
+        <x:v>DAY</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>Router Máy 2</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>MODEL-A</x:v>
+      </x:c>
+      <x:c r="G13" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M13" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="N13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="O13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P13" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="Q13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R13" t="str">
+        <x:v>setup</x:v>
+      </x:c>
+      <x:c r="S13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T13" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="U13" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="V13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W13"/>
+      <x:c r="X13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Y13" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="Z13" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AA13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB13"/>
+      <x:c r="AC13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AD13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AE13" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AF13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG13"/>
+      <x:c r="AH13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AI13" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AJ13" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="AK13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="C14"/>
+      <x:c r="D14" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="F14"/>
+      <x:c r="G14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" t="str">
+        <x:v>#DIV/0!</x:v>
+      </x:c>
+      <x:c r="N14"/>
+      <x:c r="O14"/>
+      <x:c r="P14"/>
+      <x:c r="Q14"/>
+      <x:c r="R14"/>
+      <x:c r="S14"/>
+      <x:c r="T14"/>
+      <x:c r="U14"/>
+      <x:c r="V14"/>
+      <x:c r="W14"/>
+      <x:c r="X14"/>
+      <x:c r="Y14"/>
+      <x:c r="Z14"/>
+      <x:c r="AA14"/>
+      <x:c r="AB14"/>
+      <x:c r="AC14"/>
+      <x:c r="AD14"/>
+      <x:c r="AE14"/>
+      <x:c r="AF14"/>
+      <x:c r="AG14"/>
+      <x:c r="AH14"/>
+      <x:c r="AI14"/>
+      <x:c r="AJ14"/>
+      <x:c r="AK14"/>
+      <x:c r="AL14"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A2:T2"/>
+    <x:mergeCell ref="C2:AW2"/>
+    <x:mergeCell ref="N3:AL3"/>
+    <x:mergeCell ref="N4:R4"/>
+    <x:mergeCell ref="S4:W4"/>
+    <x:mergeCell ref="X4:AB4"/>
+    <x:mergeCell ref="AC4:AG4"/>
+    <x:mergeCell ref="AH4:AL4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/smd-process-control/tests/fixtures/production-sample.xlsx
+++ b/smd-process-control/tests/fixtures/production-sample.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25.07" sheetId="1" r:id="R8f4886b525cb44de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25.07" sheetId="1" r:id="Rd6c7634fcb7446e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -607,8 +607,8 @@
       <x:c r="T7" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="U7" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="U7" t="n">
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="V7" t="n">
         <x:v>0</x:v>
@@ -620,8 +620,8 @@
       <x:c r="Y7" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Z7" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="Z7" t="n">
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AA7" t="n">
         <x:v>0</x:v>
@@ -633,8 +633,8 @@
       <x:c r="AD7" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE7" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AE7" t="n">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AF7" t="n">
         <x:v>0</x:v>
@@ -646,8 +646,8 @@
       <x:c r="AI7" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AJ7" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AJ7" t="n">
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="AK7" t="n">
         <x:v>0</x:v>
@@ -688,8 +688,8 @@
       <x:c r="O8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P8" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="P8" t="n">
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="Q8" t="n">
         <x:v>5</x:v>
@@ -703,8 +703,8 @@
       <x:c r="T8" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="U8" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="U8" t="n">
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="V8" t="n">
         <x:v>0</x:v>
@@ -716,8 +716,8 @@
       <x:c r="Y8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Z8" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="Z8" t="n">
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AA8" t="n">
         <x:v>0</x:v>
@@ -729,8 +729,8 @@
       <x:c r="AD8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE8" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AE8" t="n">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AF8" t="n">
         <x:v>0</x:v>
@@ -742,8 +742,8 @@
       <x:c r="AI8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AJ8" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AJ8" t="n">
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="AK8" t="n">
         <x:v>0</x:v>
@@ -784,8 +784,8 @@
       <x:c r="O9" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P9" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="P9" t="n">
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="Q9" t="n">
         <x:v>5</x:v>
@@ -799,8 +799,8 @@
       <x:c r="T9" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="U9" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="U9" t="n">
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="V9" t="n">
         <x:v>0</x:v>
@@ -812,8 +812,8 @@
       <x:c r="Y9" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Z9" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="Z9" t="n">
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AA9" t="n">
         <x:v>0</x:v>
@@ -825,8 +825,8 @@
       <x:c r="AD9" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE9" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AE9" t="n">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AF9" t="n">
         <x:v>0</x:v>
@@ -838,8 +838,8 @@
       <x:c r="AI9" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AJ9" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AJ9" t="n">
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="AK9" t="n">
         <x:v>0</x:v>
@@ -880,8 +880,8 @@
       <x:c r="O10" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P10" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="P10" t="n">
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="Q10" t="n">
         <x:v>5</x:v>
@@ -895,8 +895,8 @@
       <x:c r="T10" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="U10" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="U10" t="n">
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="V10" t="n">
         <x:v>0</x:v>
@@ -908,8 +908,8 @@
       <x:c r="Y10" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Z10" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="Z10" t="n">
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AA10" t="n">
         <x:v>0</x:v>
@@ -921,8 +921,8 @@
       <x:c r="AD10" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE10" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AE10" t="n">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AF10" t="n">
         <x:v>0</x:v>
@@ -934,8 +934,8 @@
       <x:c r="AI10" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AJ10" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AJ10" t="n">
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="AK10" t="n">
         <x:v>0</x:v>
@@ -976,8 +976,8 @@
       <x:c r="O11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P11" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="P11" t="n">
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="Q11" t="n">
         <x:v>5</x:v>
@@ -991,8 +991,8 @@
       <x:c r="T11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="U11" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="U11" t="n">
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="V11" t="n">
         <x:v>0</x:v>
@@ -1004,8 +1004,8 @@
       <x:c r="Y11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Z11" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="Z11" t="n">
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AA11" t="n">
         <x:v>0</x:v>
@@ -1017,8 +1017,8 @@
       <x:c r="AD11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE11" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AE11" t="n">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AF11" t="n">
         <x:v>0</x:v>
@@ -1030,8 +1030,8 @@
       <x:c r="AI11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AJ11" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AJ11" t="n">
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="AK11" t="n">
         <x:v>0</x:v>
@@ -1072,8 +1072,8 @@
       <x:c r="O12" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P12" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="P12" t="n">
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="Q12" t="n">
         <x:v>5</x:v>
@@ -1087,8 +1087,8 @@
       <x:c r="T12" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="U12" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="U12" t="n">
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="V12" t="n">
         <x:v>0</x:v>
@@ -1100,8 +1100,8 @@
       <x:c r="Y12" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Z12" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="Z12" t="n">
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AA12" t="n">
         <x:v>0</x:v>
@@ -1113,8 +1113,8 @@
       <x:c r="AD12" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE12" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AE12" t="n">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AF12" t="n">
         <x:v>0</x:v>
@@ -1126,8 +1126,8 @@
       <x:c r="AI12" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AJ12" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AJ12" t="n">
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="AK12" t="n">
         <x:v>0</x:v>
@@ -1168,8 +1168,8 @@
       <x:c r="O13" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P13" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="P13" t="n">
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="Q13" t="n">
         <x:v>5</x:v>
@@ -1183,8 +1183,8 @@
       <x:c r="T13" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="U13" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="U13" t="n">
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="V13" t="n">
         <x:v>0</x:v>
@@ -1196,8 +1196,8 @@
       <x:c r="Y13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Z13" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="Z13" t="n">
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="AA13" t="n">
         <x:v>0</x:v>
@@ -1209,8 +1209,8 @@
       <x:c r="AD13" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AE13" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AE13" t="n">
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="AF13" t="n">
         <x:v>0</x:v>
@@ -1222,8 +1222,8 @@
       <x:c r="AI13" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AJ13" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="AJ13" t="n">
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="AK13" t="n">
         <x:v>0</x:v>
@@ -1253,8 +1253,8 @@
       <x:c r="L14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" t="str">
-        <x:v>#DIV/0!</x:v>
+      <x:c r="M14" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N14"/>
       <x:c r="O14"/>
